--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4492753623188406</v>
+        <v>0.4408602150537634</v>
       </c>
       <c r="B2">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="C2">
-        <v>0.5633802816901409</v>
+        <v>0.4366197183098591</v>
       </c>
       <c r="D2">
-        <v>0.6595744680851063</v>
+        <v>0.6611570247933884</v>
       </c>
       <c r="E2">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>48</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Mistral-7B-Instruct-v0.2/Qwen3-4B-Instruct-2507/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.4408602150537634</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.4366197183098591</v>
+        <v>0.4225352112676056</v>
       </c>
       <c r="D2">
-        <v>0.6611570247933884</v>
+        <v>0.6507936507936508</v>
       </c>
       <c r="E2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
